--- a/administrative_forms/007_laptop_requisition_form--administrative_forms.xlsx
+++ b/administrative_forms/007_laptop_requisition_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'apple_macbook_13',_'value':_'apple_macbook_13'}</t>
+          <t>apple_macbook_13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Apple MacBook 13', 'value': 'apple_macbook_13'}</t>
+          <t>Apple MacBook 13</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'lenovo_thinkpad',_'value':_'lenovo_thinkpad'}</t>
+          <t>lenovo_thinkpad</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Lenovo ThinkPad', 'value': 'lenovo_thinkpad'}</t>
+          <t>Lenovo ThinkPad</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'dell_xps',_'value':_'dell_xps'}</t>
+          <t>dell_xps</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Dell XPS', 'value': 'dell_xps'}</t>
+          <t>Dell XPS</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'sales',_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Sales', 'value': 'sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing', 'value': 'marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'it',_'value':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'IT', 'value': 'it'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'customer_service',_'value':_'customer_service'}</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Service', 'value': 'customer_service'}</t>
+          <t>Customer Service</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'it',_'value':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'IT', 'value': 'it'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'department_manager',_'value':_'department_manager'}</t>
+          <t>department_manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Department Manager', 'value': 'department_manager'}</t>
+          <t>Department Manager</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'team_lead',_'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Team Lead', 'value': 'team_lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'sales',_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Sales', 'value': 'sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing', 'value': 'marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'it',_'value':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'IT', 'value': 'it'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'customer_service',_'value':_'customer_service'}</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Service', 'value': 'customer_service'}</t>
+          <t>Customer Service</t>
         </is>
       </c>
     </row>
